--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WEST_VIRGINIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WEST_VIRGINIA_2013.xlsx
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C105">
